--- a/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_waerzeggersMouseModelsNeurological2010.xlsx
+++ b/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_waerzeggersMouseModelsNeurological2010.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sdoneva/Documents/Work/In Progress/PhD/PhD Projects/In Progress/Preclinical_Pipeline/03_IE_tasks/data/related/outcomes_endpoints/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C817737-E121-B342-8A57-FBB5015F84CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC3FFCE-010A-F04B-86B2-415AB0BA9300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35720" yWindow="4500" windowWidth="27640" windowHeight="16940" xr2:uid="{56AF2C6D-1F90-4F42-AFE2-C1F9BE815D6D}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{56AF2C6D-1F90-4F42-AFE2-C1F9BE815D6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="77">
   <si>
     <t>Test Name</t>
   </si>
@@ -53,18 +53,12 @@
     <t>Gray-matter volume/atrophy (voxel-based morphometry)</t>
   </si>
   <si>
-    <t>Imaging &amp; Morphology</t>
-  </si>
-  <si>
     <t>Resting‐state fMRI (BOLD)</t>
   </si>
   <si>
     <t>Functional connectivity and activation patterns in motor/cognitive circuits</t>
   </si>
   <si>
-    <t>Physiological &amp; Metabolic</t>
-  </si>
-  <si>
     <t>MR Spectroscopy (MRS)</t>
   </si>
   <si>
@@ -75,9 +69,6 @@
   </si>
   <si>
     <t>Presynaptic aromatic-amino-acid-decarboxylase activity and vesicular storage</t>
-  </si>
-  <si>
-    <t>Molecular &amp; Cellular</t>
   </si>
   <si>
     <t>Dopamine‐transporter binding density</t>
@@ -284,6 +275,9 @@
   </si>
   <si>
     <t>Transgene‐driven tracer phosphorylation or retention (tumor cell localization)</t>
+  </si>
+  <si>
+    <t>Imaging</t>
   </si>
 </sst>
 </file>
@@ -682,7 +676,10 @@
   <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="58.5" customWidth="1"/>
+    <col min="1" max="1" width="42.83203125" customWidth="1"/>
+    <col min="2" max="2" width="55.33203125" customWidth="1"/>
+    <col min="3" max="3" width="33.83203125" customWidth="1"/>
+    <col min="4" max="4" width="28.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -704,403 +701,403 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C27" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C31" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C34" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
